--- a/Codes_2025/Trial 3/Trial3_Proposed (ElasticNet)_Leaders_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_Proposed (ElasticNet)_Leaders_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
         <v>99.25285121909999</v>
       </c>
       <c r="F2" t="n">
-        <v>72.19434356689453</v>
+        <v>74.02732849121094</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,23 +504,23 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>80.48732126890965</v>
+        <v>81.63099697043461</v>
       </c>
       <c r="I2" t="n">
-        <v>10.95732126890958</v>
+        <v>12.10099697043454</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>37.67999999999999</v>
+        <v>37.81</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>50.54610131507693</v>
+        <v>37.22033627553438</v>
       </c>
       <c r="F3" t="n">
-        <v>39.14875411987305</v>
+        <v>52.13083267211914</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -539,23 +539,23 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>42.93728356196682</v>
+        <v>47.44607076874917</v>
       </c>
       <c r="I3" t="n">
-        <v>5.25728356196683</v>
+        <v>9.636070768749171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>37.58000000000002</v>
+        <v>37.67999999999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -563,10 +563,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>25.1977926501113</v>
+        <v>50.54610131507693</v>
       </c>
       <c r="F4" t="n">
-        <v>50.92008972167969</v>
+        <v>44.13265228271484</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -574,23 +574,23 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>41.00996264737107</v>
+        <v>46.19666140971184</v>
       </c>
       <c r="I4" t="n">
-        <v>3.429962647371049</v>
+        <v>8.516661409711844</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>35.4</v>
+        <v>37.58000000000002</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>54.79771450242716</v>
+        <v>25.1977926501113</v>
       </c>
       <c r="F5" t="n">
-        <v>57.92023086547852</v>
+        <v>52.79691696166992</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -609,23 +609,23 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>55.87509457102158</v>
+        <v>44.14223285597578</v>
       </c>
       <c r="I5" t="n">
-        <v>20.47509457102158</v>
+        <v>6.562232855975765</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>22.34</v>
+        <v>35.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21.49547930685887</v>
+        <v>54.79771450242716</v>
       </c>
       <c r="F6" t="n">
-        <v>11.66981887817383</v>
+        <v>39.86308670043945</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -644,23 +644,23 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>15.81686329323426</v>
+        <v>44.63597683178405</v>
       </c>
       <c r="I6" t="n">
-        <v>6.523136706765733</v>
+        <v>9.23597683178405</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>21.01</v>
+        <v>24.26000000000001</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -668,10 +668,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22.46325384117893</v>
+        <v>36.70529760187497</v>
       </c>
       <c r="F7" t="n">
-        <v>20.93357467651367</v>
+        <v>33.35495376586914</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -679,23 +679,23 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>21.79655552066289</v>
+        <v>34.58319766897615</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7865555206628905</v>
+        <v>10.32319766897615</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>20.08</v>
+        <v>22.34</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14.5973875851344</v>
+        <v>21.49547930685887</v>
       </c>
       <c r="F8" t="n">
-        <v>15.41469097137451</v>
+        <v>21.26105880737305</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -714,23 +714,23 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>15.62164445673074</v>
+        <v>21.65179483461739</v>
       </c>
       <c r="I8" t="n">
-        <v>4.45835554326926</v>
+        <v>0.6882051653826018</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>10.19</v>
+        <v>21.01</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8.511111330196202</v>
+        <v>22.46325384117893</v>
       </c>
       <c r="F9" t="n">
-        <v>8.670866012573242</v>
+        <v>23.09369659423828</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -749,23 +749,23 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9.339715723136665</v>
+        <v>23.19380980475951</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8502842768633325</v>
+        <v>2.183809804759505</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>9.359999999999999</v>
+        <v>20.08</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -773,10 +773,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9.622454454199397</v>
+        <v>14.5973875851344</v>
       </c>
       <c r="F10" t="n">
-        <v>10.83236885070801</v>
+        <v>14.89854907989502</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -784,23 +784,23 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>11.05232865723155</v>
+        <v>15.19334084288337</v>
       </c>
       <c r="I10" t="n">
-        <v>1.692328657231547</v>
+        <v>4.886659157116625</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>7.73</v>
+        <v>10.19</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.922944893692857</v>
+        <v>8.511111330196202</v>
       </c>
       <c r="F11" t="n">
-        <v>2.552172899246216</v>
+        <v>7.499971866607666</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -819,23 +819,23 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3.258020559465971</v>
+        <v>8.287495846432087</v>
       </c>
       <c r="I11" t="n">
-        <v>4.471979440534028</v>
+        <v>1.902504153567911</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>7.180000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.570951940213813</v>
+        <v>9.622454454199397</v>
       </c>
       <c r="F12" t="n">
-        <v>4.177378177642822</v>
+        <v>12.97760963439941</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -854,23 +854,23 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.553683764458911</v>
+        <v>12.34021712254676</v>
       </c>
       <c r="I12" t="n">
-        <v>1.62631623554109</v>
+        <v>2.980217122546762</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>6.590000000000001</v>
+        <v>7.73</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -878,10 +878,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.058388586643492</v>
+        <v>1.922944893692857</v>
       </c>
       <c r="F13" t="n">
-        <v>8.504582405090332</v>
+        <v>2.524525165557861</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -889,45 +889,150 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>8.717947259085944</v>
+        <v>2.864186009430855</v>
       </c>
       <c r="I13" t="n">
-        <v>2.127947259085944</v>
+        <v>4.865813990569144</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7.180000000000001</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5.570951940213813</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.73715353012085</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>5.500261721841874</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.679738278158126</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.81</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>10.71820080519103</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9.963083267211914</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>10.64304970587133</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.833049705871329</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6.590000000000001</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>7.058388586643492</v>
+      </c>
+      <c r="F16" t="n">
+        <v>8.4263916015625</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>8.460564097175153</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.870564097175152</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="n">
         <v>6.549999999999999</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>6.9664063060335</v>
       </c>
-      <c r="F14" t="n">
-        <v>6.184333324432373</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Leaders</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>7.274149947592814</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.7241499475928155</v>
+      <c r="F17" t="n">
+        <v>7.733612537384033</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>7.963168824061419</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.41316882406142</v>
       </c>
     </row>
   </sheetData>
